--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_153_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_153_R16.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4399</v>
+        <v>3.4041</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0585</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3815</v>
+        <v>3.3142</v>
       </c>
       <c r="G2" t="n">
         <v>1.1527</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7178</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6097</v>
+        <v>0.6411</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1081</v>
+        <v>0.0409</v>
       </c>
       <c r="V2" t="n">
         <v>-1.214</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3114</v>
+        <v>3.1172</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7997</v>
+        <v>0.8744</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5117</v>
+        <v>2.2429</v>
       </c>
       <c r="G3" t="n">
         <v>0.9321</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3198</v>
+        <v>0.1256</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1845</v>
+        <v>-0.1098</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5043</v>
+        <v>0.2355</v>
       </c>
       <c r="V3" t="n">
         <v>4.147</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6788</v>
+        <v>1.6259</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1087</v>
+        <v>0.0221</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5701</v>
+        <v>1.6037</v>
       </c>
       <c r="G4" t="n">
         <v>1.2158</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4494</v>
+        <v>-0.5023</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0351</v>
+        <v>-0.1217</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4143</v>
+        <v>-0.3806</v>
       </c>
       <c r="V4" t="n">
         <v>1.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.023</v>
+        <v>1.2499</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1815</v>
+        <v>0.247</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2045</v>
+        <v>1.0029</v>
       </c>
       <c r="G5" t="n">
         <v>4.5395</v>
@@ -844,13 +844,13 @@
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2153</v>
+        <v>0.4422</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1968</v>
+        <v>0.6253</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0185</v>
+        <v>-0.1832</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2525</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.0052</v>
       </c>
       <c r="E6" t="n">
         <v>1.5339</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5958</v>
+        <v>-0.5286</v>
       </c>
       <c r="G6" t="n">
         <v>1.0584</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3523</v>
+        <v>-0.2851</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3523</v>
+        <v>-0.2851</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.852</v>
+        <v>-0.0237</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5334</v>
+        <v>-1.2412</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3855</v>
+        <v>1.2174</v>
       </c>
       <c r="G7" t="n">
         <v>0.1163</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7357</v>
+        <v>0.8599</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3566</v>
+        <v>0.6488</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3791</v>
+        <v>0.2111</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1706</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5108</v>
+        <v>-1.3929</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3403</v>
+        <v>0.4075</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0556</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.651</v>
+        <v>-0.4659</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3863</v>
+        <v>-1.2704</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2976</v>
+        <v>-1.0938</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9112</v>
+        <v>-0.1766</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7968</v>
+        <v>2.9149</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0095</v>
+        <v>1.6903</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8063</v>
+        <v>1.2246</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7292</v>
+        <v>2.5147</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7661</v>
+        <v>1.1798</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>1.3349</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.4002</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7756</v>
+        <v>0.5105</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8431</v>
+        <v>-0.1103</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0876</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>-3.7112</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>1.498</v>
+        <v>-0.1131</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9109</v>
+        <v>-0.0391</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4129</v>
+        <v>-0.074</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6809</v>
+        <v>-1.3777</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6448</v>
+        <v>-2.4089</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9639</v>
+        <v>1.0311</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8083</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1046</v>
+        <v>0.1986</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0668</v>
+        <v>0.1691</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0378</v>
+        <v>0.0294</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4299</v>
+        <v>-2.8018</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9509</v>
+        <v>-3.713</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4791</v>
+        <v>0.9112</v>
       </c>
       <c r="G11" t="n">
-        <v>2.9149</v>
+        <v>-0.7968</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6903</v>
+        <v>0.0095</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2246</v>
+        <v>-0.8063</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5147</v>
+        <v>-0.7292</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1798</v>
+        <v>-0.7661</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3349</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4002</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5105</v>
+        <v>0.7756</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1103</v>
+        <v>-0.8431</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.7112</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2727</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8962</v>
+        <v>0.4955</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3765</v>
+        <v>-0.4129</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0567</v>
+        <v>-3.6777</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2082</v>
+        <v>0.0027</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8485</v>
+        <v>-3.6805</v>
       </c>
       <c r="G12" t="n">
         <v>0.3807</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9889</v>
+        <v>0.3901</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7389</v>
+        <v>0.472</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.25</v>
+        <v>-0.0819</v>
       </c>
       <c r="V12" t="n">
         <v>-3.7527</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4812999999999992</v>
+        <v>0.2655999999999996</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.826399999999999</v>
+        <v>-7.0798</v>
       </c>
       <c r="F13" t="n">
-        <v>7.3453</v>
+        <v>7.3452</v>
       </c>
       <c r="G13" t="n">
         <v>9.649699999999999</v>
@@ -1468,16 +1468,16 @@
         <v>17.3965</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6677000000000001</v>
+        <v>1.4146</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9285</v>
+        <v>2.6751</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2608</v>
+        <v>-1.2606</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.6805</v>
+        <v>-2.680499999999999</v>
       </c>
       <c r="W13" t="n">
         <v>7.9308</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.7738</v>
+        <v>5.1896</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1364</v>
+        <v>4.4851</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6374</v>
+        <v>0.7046</v>
       </c>
       <c r="G14" t="n">
         <v>1.6454</v>
@@ -1546,13 +1546,13 @@
         <v>3.2473</v>
       </c>
       <c r="S14" t="n">
-        <v>2.113</v>
+        <v>0.5289</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1745</v>
+        <v>0.5232</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0615</v>
+        <v>0.0057</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6036</v>
+        <v>2.4679</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1955</v>
+        <v>0.2763</v>
       </c>
       <c r="F15" t="n">
-        <v>1.799</v>
+        <v>2.1916</v>
       </c>
       <c r="G15" t="n">
         <v>-2.1207</v>
@@ -1624,13 +1624,13 @@
         <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5979</v>
+        <v>0.2664</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3339</v>
+        <v>0.1379</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.264</v>
+        <v>0.1285</v>
       </c>
       <c r="V15" t="n">
         <v>2.0026</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9133</v>
+        <v>0.8353</v>
       </c>
       <c r="E16" t="n">
         <v>1.4196</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5063</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4116</v>
@@ -1702,13 +1702,13 @@
         <v>3.7112</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.1601</v>
       </c>
       <c r="T16" t="n">
         <v>0.1537</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2359</v>
+        <v>-0.3139</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8667</v>
+        <v>0.0639</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5672</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2995</v>
+        <v>0.0639</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0092</v>
+        <v>0.1465</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-0.168</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1639</v>
+        <v>0.3145</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1488</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4769</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6257</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1581</v>
+        <v>0.1465</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3684</v>
+        <v>-0.168</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7896</v>
+        <v>0.3145</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8038</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.274</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5298</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0639</v>
+        <v>-0.0426</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.1405</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0639</v>
+        <v>0.0979</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1465</v>
+        <v>-1.0092</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.168</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3145</v>
+        <v>-0.1639</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.1488</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.4769</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6257</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1465</v>
+        <v>-1.1581</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.168</v>
+        <v>-0.3684</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3145</v>
+        <v>-0.7896</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.8944</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.5663</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.3282</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7684</v>
+        <v>-0.454</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4875</v>
+        <v>-2.6096</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7191</v>
+        <v>2.1556</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3466</v>
+        <v>-1.2669</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1525</v>
+        <v>-1.5714</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1941</v>
+        <v>0.3045</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0536</v>
+        <v>-1.2065</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>-1.9893</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.293</v>
+        <v>-0.0604</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1357</v>
+        <v>0.4179</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>-0.4783</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>3.0154</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4191</v>
+        <v>-0.8107</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>-0.0114</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2697</v>
+        <v>-0.7993</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1839</v>
+        <v>-0.4652</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0814</v>
+        <v>-1.2516</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8975</v>
+        <v>0.7863</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2669</v>
+        <v>0.3466</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5714</v>
+        <v>0.1525</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3045</v>
+        <v>0.1941</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2065</v>
+        <v>0.0536</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9893</v>
+        <v>0.0168</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0604</v>
+        <v>0.293</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4179</v>
+        <v>0.1357</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4783</v>
+        <v>0.1573</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0154</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5406</v>
+        <v>-0.116</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4832</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0574</v>
+        <v>-0.2025</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6783</v>
+        <v>-0.891</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2609</v>
+        <v>-1.3999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5825</v>
+        <v>0.5089</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.418</v>
+        <v>-0.1402</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2401</v>
+        <v>0.7499</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1779</v>
+        <v>-0.8901</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1123</v>
+        <v>1.1609</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3592</v>
+        <v>1.3618</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7531</v>
+        <v>-0.201</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3057</v>
+        <v>-1.3011</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8809</v>
+        <v>-0.612</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4248</v>
+        <v>-0.6891</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8556</v>
+        <v>-6.0307</v>
       </c>
       <c r="R21" t="n">
-        <v>3.4793</v>
+        <v>3.2473</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5619</v>
+        <v>-0.5061</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9709</v>
+        <v>-0.2827</v>
       </c>
       <c r="U21" t="n">
-        <v>0.409</v>
+        <v>-0.2234</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.5387</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6778999999999999</v>
+        <v>3.7527</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7196</v>
+        <v>-0.9618</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0972</v>
+        <v>-2.5074</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3776</v>
+        <v>1.5457</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1361</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.1994</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5975</v>
+        <v>-0.0077</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V22" t="n">
         <v>1.214</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8431</v>
+        <v>-1.2059</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8846</v>
+        <v>-2.5532</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0414</v>
+        <v>1.3473</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2855</v>
+        <v>-3.418</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5666</v>
+        <v>-2.2401</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2811</v>
+        <v>-1.1779</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4068</v>
+        <v>-1.1123</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4804</v>
+        <v>-0.3592</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0736</v>
+        <v>-0.7531</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1213</v>
+        <v>-2.3057</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0862</v>
+        <v>-1.8809</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2075</v>
+        <v>-0.4248</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0154</v>
+        <v>-1.8556</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3195</v>
+        <v>3.4793</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8187</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5375</v>
+        <v>-0.2631</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2812</v>
+        <v>0.1737</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.6805</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5467</v>
+        <v>-3.2687</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4614</v>
+        <v>-3.0641</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0853</v>
+        <v>-0.2046</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1402</v>
+        <v>-0.2855</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7499</v>
+        <v>-0.5666</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8901</v>
+        <v>0.2811</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1609</v>
+        <v>-0.4068</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3618</v>
+        <v>-0.4804</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.201</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3011</v>
+        <v>0.1213</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.612</v>
+        <v>-0.0862</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6891</v>
+        <v>0.2075</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.7834</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.0307</v>
+        <v>-3.0154</v>
       </c>
       <c r="R24" t="n">
-        <v>3.2473</v>
+        <v>2.3195</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1618</v>
+        <v>0.3932</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3443</v>
+        <v>0.358</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8175</v>
+        <v>0.0351</v>
       </c>
       <c r="V24" t="n">
-        <v>2.5387</v>
+        <v>-2.6805</v>
       </c>
       <c r="W24" t="n">
-        <v>3.7527</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.214</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4813000000000005</v>
+        <v>1.267500000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-7.3453</v>
       </c>
       <c r="F25" t="n">
-        <v>7.8263</v>
+        <v>8.613000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-9.649700000000001</v>
@@ -2380,7 +2380,7 @@
         <v>-1.821</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.693900000000001</v>
+        <v>-3.6939</v>
       </c>
       <c r="L25" t="n">
         <v>1.8728</v>
@@ -2389,13 +2389,13 @@
         <v>-7.8287</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.902000000000001</v>
+        <v>-4.902</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.926699999999999</v>
+        <v>-2.9267</v>
       </c>
       <c r="P25" t="n">
-        <v>8.118399999999999</v>
+        <v>8.118400000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.3965</v>
@@ -2404,13 +2404,13 @@
         <v>25.5147</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6677000000000004</v>
+        <v>0.1186000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2605</v>
+        <v>1.2607</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.928399999999999</v>
+        <v>-1.1423</v>
       </c>
       <c r="V25" t="n">
         <v>2.6805</v>
